--- a/labs/lab-04-workbook-rules/data/checkpoints/Northstar_Verified_Checkpoint.xlsx
+++ b/labs/lab-04-workbook-rules/data/checkpoints/Northstar_Verified_Checkpoint.xlsx
@@ -13,16 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt_Log" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name=".Rules" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence_Log" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name=".Rules" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'About_This_Data'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Work_Orders'!$A$1:$M$121</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Technicians'!$A$1:$D$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Control'!$A$1:$B$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Prompt_Log'!$A$1:$F$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Checks'!$A$1:$C$2</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -562,7 +556,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1332,7 +1325,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr"/>
+      <c r="F14" s="2"/>
       <c r="G14" s="4" t="n">
         <v>46278</v>
       </c>
@@ -1972,7 +1965,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr"/>
+      <c r="F26" s="2"/>
       <c r="G26" s="4" t="n">
         <v>46266</v>
       </c>
@@ -3260,7 +3253,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr"/>
+      <c r="F50" s="2"/>
       <c r="G50" s="4" t="n">
         <v>46242</v>
       </c>
@@ -4548,7 +4541,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr"/>
+      <c r="F74" s="2"/>
       <c r="G74" s="4" t="n">
         <v>46218</v>
       </c>
@@ -5188,7 +5181,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr"/>
+      <c r="F86" s="2"/>
       <c r="G86" s="4" t="n">
         <v>46286</v>
       </c>
@@ -6476,7 +6469,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr"/>
+      <c r="F110" s="2"/>
       <c r="G110" s="4" t="n">
         <v>46262</v>
       </c>
@@ -7091,7 +7084,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M121"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7297,7 +7289,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7479,7 +7470,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7559,12 +7549,36 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>EXCEL - PLAN</t>
+          <t>EXCEL - ALLOW EDITING</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EXCEL - PLAN:
+          <t>EXCEL - ALLOW EDITING:
+Add a visible worksheet named exactly .Rules (with the leading dot) as the last tab; if it exists, clear column A and reuse it. Fill column A only, one cell per line below, entering only the text after each "A#: " label. Do not change any other sheet.
+A1: ## SOURCE AND SCOPE
+A2: Preserve Work_Orders, tblWorkOrders, Technicians, current Assigned_To values and source IDs.
+A3: Use the reporting date from Control!B2. State the selected Site, Job_Category, Status and Assigned_To scope beside every report.
+A4: Backlog excludes Closed and Cancelled. Overdue backlog has Due_Date strictly before Control!B2.
+A5: On-time closure rate uses Closed rows only, with Closed_Date &lt;= Due_Date. Display N/A when no Closed rows remain.
+A6: ## FORMATS AND VISUALS
+A7: Display recorded Cost_SGD as S$ with two decimals; keep underlying values exact. Show dates as DD-MMM-YYYY.
+A8: Use white backgrounds, navy titles, blue and teal accents, readable labels and named units; never use colour alone.
+A9: ## DASHBOARD LAYOUT
+A10: Dashboard sheet: title in A1; Site, Job_Category, Status and Assigned_To dropdowns in B2:B5 (All plus source values); the six measures in B7:B12; data-as-at date and selected scope in D2.
+A11: Six KPI tiles in D4:I7, one column per tile: title in row 4, large value in row 5, short definition in row 6 and "Checks: PASS" in row 7.
+A12: Charts in a grid below the tiles: work orders by status and by job category side by side, then a full-width stacked bar by site (overdue backlog, other backlog, Closed, Cancelled).
+A13: Slicers for Site, Job_Category, Status and Assigned_To on the right of the tiles, connected to tblWorkOrders. KPI formulas use SUBTOTAL visibility so slicers and dropdowns both filter every tile and chart.
+A14: Put chart summaries, chart-title formulas and KPI checks on Dashboard_Summaries. Never merge cells. Hide gridlines on Dashboard.
+A15: ## DASHBOARD STYLE
+A16: Tiles: white bold text on solid navy #1F4E79 (totals and rates), blue #2E75B6 (backlog, overdue) or teal #2A9D8F (Closed, cost).
+A17: Every chart title states the finding from a cell formula, e.g. "Changi Workshop has the most overdue backlog (18 of 50)".
+A18: Show data labels on bars; no gridlines; rates as % with one decimal. Each chart total must equal B7.
+A19: ## OUTPUT AND REVIEW
+A20: Use structured table references. Preserve the visible .Rules sheet and unrelated sheets, charts and Prompt_Log.
+A21: Keep current owners separate from unapproved assignment proposals. Missing facts and approvals remain UNKNOWN.
+A22: Ask before replacing named output sheets. Reconcile every count, rate and chart against source rows; do not duplicate outputs on rerun.
+EXCEL - PLAN:
 Review the visible .Rules column A for this Northstar workbook. Identify ambiguous instructions or conflicts with the actual source and Control. Propose concise corrections, keeping one idea per cell. Do not edit the source or invent precedence between rules, preferences and Skills.</t>
         </is>
       </c>
@@ -7642,7 +7656,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7686,12 +7699,10 @@
       </c>
       <c r="B2" s="2">
         <f>ROWS(tblWorkOrders[Work_Order_ID])</f>
-        <v/>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
+      </c>
+      <c r="C2" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7702,7 +7713,79 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Claim_or_Test</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Observed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source_and_Scope</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>As_At</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Verified_By</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -7767,35 +7850,104 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>## OUTPUT AND REVIEW</t>
+          <t>## DASHBOARD LAYOUT</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Use structured table references. Preserve the visible .Rules sheet and unrelated sheets, charts and Prompt_Log.</t>
+          <t>Dashboard sheet: title in A1; Site, Job_Category, Status and Assigned_To dropdowns in B2:B5 (All plus source values); the six measures in B7:B12; data-as-at date and selected scope in D2.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Keep current owners separate from unapproved assignment proposals. Missing facts and approvals remain UNKNOWN.</t>
+          <t>Six KPI tiles in D4:I7, one column per tile: title in row 4, large value in row 5, short definition in row 6 and "Checks: PASS" in row 7.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>Charts in a grid below the tiles: work orders by status and by job category side by side, then a full-width stacked bar by site (overdue backlog, other backlog, Closed, Cancelled).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Slicers for Site, Job_Category, Status and Assigned_To on the right of the tiles, connected to tblWorkOrders. KPI formulas use SUBTOTAL visibility so slicers and dropdowns both filter every tile and chart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Put chart summaries, chart-title formulas and KPI checks on Dashboard_Summaries. Never merge cells. Hide gridlines on Dashboard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>## DASHBOARD STYLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Tiles: white bold text on solid navy #1F4E79 (totals and rates), blue #2E75B6 (backlog, overdue) or teal #2A9D8F (Closed, cost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Every chart title states the finding from a cell formula, e.g. "Changi Workshop has the most overdue backlog (18 of 50)".</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Show data labels on bars; no gridlines; rates as % with one decimal. Each chart total must equal B7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>## OUTPUT AND REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Use structured table references. Preserve the visible .Rules sheet and unrelated sheets, charts and Prompt_Log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Keep current owners separate from unapproved assignment proposals. Missing facts and approvals remain UNKNOWN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
           <t>Ask before replacing named output sheets. Reconcile every count, rate and chart against source rows; do not duplicate outputs on rerun.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2">
+    <row r="23">
+      <c r="A23" s="2">
         <f>"Reporting date: "&amp;TEXT(Control!B2,"yyyy-mm-dd")</f>
-        <v/>
       </c>
     </row>
   </sheetData>
